--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Race.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Race.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -1293,88 +1293,88 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>goblin</t>
+          <t>ratkin</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>EA 23.289</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>ratoide</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>goblin</t>
+          <t>ratkin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ゴブリン</t>
+          <t>ラトキン</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kobolt</t>
+          <t>werewolf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.293</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kobold</t>
+          <t>lobisomem</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>kobold</t>
+          <t>werewolf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>コボルト</t>
+          <t>人狼</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>goblin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orc</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>goblin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>オーク</t>
+          <t>ゴブリン</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>troll</t>
+          <t>kobolt</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1384,24 +1384,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Troll</t>
+          <t>Kobold</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>troll</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>トロール</t>
+          <t>コボルト</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lizardman</t>
+          <t>orc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1411,24 +1411,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Homem-Lagarto</t>
+          <t>Orc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>lizardman</t>
+          <t>orc</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>リザードマン</t>
+          <t>オーク</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>minotaur</t>
+          <t>troll</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1438,24 +1438,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minotauro</t>
+          <t>Troll</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>minotaur</t>
+          <t>troll</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ミノタウロス</t>
+          <t>トロール</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>norland</t>
+          <t>lizardman</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1465,24 +1465,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norlandês</t>
+          <t>Homem-Lagarto</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>norland</t>
+          <t>lizardman</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ノーランド</t>
+          <t>リザードマン</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>asura</t>
+          <t>minotaur</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1492,66 +1492,51 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Asura</t>
+          <t>Minotauro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>asura</t>
+          <t>minotaur</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>阿修羅</t>
+          <t>ミノタウロス</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>norland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EA 23.278</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>Norlandês</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>norland</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>スライム</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Slimes são seres amorfos e gelatinosos, com corpos que não possuem forma fixa. Podem parecer frágeis e são frequentemente chamados de os monstros mais fracos, mas possuem um potencial misterioso de absorver tudo o que ingerem e transformá-lo em sua própria força. Mesmo que você um dia acordasse como um slime, não haveria motivo para desespero. Aquele corpo humilde é apenas o começo de um caminho sem fim de evolução.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
+          <t>ノーランド</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>asura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1561,51 +1546,66 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lobo</t>
+          <t>Asura</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>asura</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>狼</t>
+          <t>阿修羅</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.278</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zumbi</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ゾンビ</t>
+          <t>スライム</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Slimes são seres amorfos e gelatinosos, com corpos que não possuem forma fixa. Podem parecer frágeis e são frequentemente chamados de os monstros mais fracos, mas possuem um potencial misterioso de absorver tudo o que ingerem e transformá-lo em sua própria força. Mesmo que você um dia acordasse como um slime, não haveria motivo para desespero. Aquele corpo humilde é apenas o começo de um caminho sem fim de evolução.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rabbit</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1615,24 +1615,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Lobo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rabbit</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ウサギ</t>
+          <t>狼</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sheep</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1642,24 +1642,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovelha</t>
+          <t>Zumbi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sheep</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>羊</t>
+          <t>ゾンビ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>frog</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1669,51 +1669,51 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>frog</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>蛙</t>
+          <t>ウサギ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>centipede</t>
+          <t>rabbitkin</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.289</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Centopeia</t>
+          <t>raviano</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>centipede</t>
+          <t>ravian</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ムカデ</t>
+          <t>ラビアン</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mandrake</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1723,51 +1723,51 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mandrágora</t>
+          <t>Ovelha</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>mandrake</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>マンドレイク</t>
+          <t>羊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>beetle</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EA 23.27 fix 2</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Besouro</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>beetle</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>甲虫</t>
+          <t>蛙</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>centipede</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1777,24 +1777,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cogumelo</t>
+          <t>Centopeia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>centipede</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>きのこ</t>
+          <t>ムカデ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bat</t>
+          <t>mandrake</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1804,51 +1804,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morcego</t>
+          <t>Mandrágora</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>bat</t>
+          <t>mandrake</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>コウモリ</t>
+          <t>マンドレイク</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ent</t>
+          <t>beetle</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.27 fix 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ent</t>
+          <t>Besouro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ent</t>
+          <t>beetle</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>エント</t>
+          <t>甲虫</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hound</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1858,24 +1858,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cão de Caça</t>
+          <t>Cogumelo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>hound</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>猟犬</t>
+          <t>きのこ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1885,24 +1885,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fantasma</t>
+          <t>Morcego</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>幽霊</t>
+          <t>コウモリ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>spirit</t>
+          <t>ent</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1912,24 +1912,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Espírito</t>
+          <t>Ent</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>spirit</t>
+          <t>ent</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>精霊</t>
+          <t>エント</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>hound</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1939,24 +1939,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Olho</t>
+          <t>Cão de Caça</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>hound</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>目</t>
+          <t>猟犬</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>wyvern</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Guiverno</t>
+          <t>Fantasma</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>wyvern</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ワイバーン</t>
+          <t>幽霊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>wasp</t>
+          <t>spirit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vespa</t>
+          <t>Espírito</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>wasp</t>
+          <t>spirit</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ワスプ</t>
+          <t>精霊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2020,24 +2020,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gigante</t>
+          <t>Olho</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>目</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>imp</t>
+          <t>wyvern</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2047,24 +2047,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Diabrete</t>
+          <t>Guiverno</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>imp</t>
+          <t>wyvern</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>インプ</t>
+          <t>ワイバーン</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>wasp</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2074,24 +2074,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mão</t>
+          <t>Vespa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>wasp</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>手</t>
+          <t>ワスプ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2101,24 +2101,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cobra</t>
+          <t>Gigante</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>蛇</t>
+          <t>巨人</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>drake</t>
+          <t>imp</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2128,24 +2128,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Draco</t>
+          <t>Diabrete</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>drake</t>
+          <t>imp</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ドレイク</t>
+          <t>インプ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2155,24 +2155,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Urso</t>
+          <t>Mão</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>手</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2182,24 +2182,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Armadura</t>
+          <t>Cobra</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>鎧</t>
+          <t>蛇</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>medusa</t>
+          <t>drake</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2209,24 +2209,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Medusa</t>
+          <t>Draco</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medusa</t>
+          <t>drake</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>メデューサ</t>
+          <t>ドレイク</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cupid</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cupido</t>
+          <t>Urso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>cupid</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>キューピット</t>
+          <t>熊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>phantom</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2263,24 +2263,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fantasma Sombrio</t>
+          <t>Armadura</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>phantom</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ファントム</t>
+          <t>鎧</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>harpy</t>
+          <t>medusa</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2290,24 +2290,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hárpia</t>
+          <t>Medusa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>harpy</t>
+          <t>medusa</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ハーピー</t>
+          <t>メデューサ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>cupid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2317,24 +2317,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dragão</t>
+          <t>Cupido</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>cupid</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ドラゴン</t>
+          <t>キューピット</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dinosaur</t>
+          <t>phantom</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2344,24 +2344,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dinossauro</t>
+          <t>Fantasma Sombrio</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>dinosaur</t>
+          <t>phantom</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>恐竜</t>
+          <t>ファントム</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cerberus</t>
+          <t>harpy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2371,24 +2371,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cérbero</t>
+          <t>Hárpia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>cerberus</t>
+          <t>harpy</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ケルベロス</t>
+          <t>ハーピー</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>spider</t>
+          <t>dragon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2398,24 +2398,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Aranha</t>
+          <t>Dragão</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>spider</t>
+          <t>dragon</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>蜘蛛</t>
+          <t>ドラゴン</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2425,24 +2425,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rocha</t>
+          <t>Dinossauro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>岩</t>
+          <t>恐竜</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>crab</t>
+          <t>cerberus</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2452,24 +2452,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Caranguejo</t>
+          <t>Cérbero</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>crab</t>
+          <t>cerberus</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>蟹</t>
+          <t>ケルベロス</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>skeleton</t>
+          <t>spider</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Esqueleto</t>
+          <t>Aranha</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>skeleton</t>
+          <t>spider</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>骸骨</t>
+          <t>蜘蛛</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2506,24 +2506,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Peça</t>
+          <t>Rocha</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>駒</t>
+          <t>岩</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>crab</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gato</t>
+          <t>Caranguejo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>crab</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>猫</t>
+          <t>蟹</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>skeleton</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2560,24 +2560,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cachorro</t>
+          <t>Esqueleto</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>skeleton</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>犬</t>
+          <t>骸骨</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>roran</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2587,51 +2587,51 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Roran</t>
+          <t>Peça</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>roran</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ローラン</t>
+          <t>駒</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mermaid</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alpha 20.64</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sereia</t>
+          <t>Gato</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>mermaid</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>人魚</t>
+          <t>猫</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rat</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2641,24 +2641,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rato</t>
+          <t>Cachorro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>rat</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ねずみ</t>
+          <t>犬</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>roran</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2668,51 +2668,51 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Concha</t>
+          <t>Roran</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>roran</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>やどかり</t>
+          <t>ローラン</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>mermaid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.64</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Máquina</t>
+          <t>Sereia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>mermaid</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>機械</t>
+          <t>人魚</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>wisp</t>
+          <t>rat</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2722,24 +2722,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fagulha</t>
+          <t>Rato</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>wisp</t>
+          <t>rat</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ウィスプ</t>
+          <t>ねずみ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2749,24 +2749,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Galinha</t>
+          <t>Concha</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>鶏</t>
+          <t>やどかり</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>stalker</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2776,24 +2776,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Perseguidor</t>
+          <t>Máquina</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>stalker</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ストーカー</t>
+          <t>機械</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>yeek</t>
+          <t>wisp</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2803,24 +2803,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yeek</t>
+          <t>Fagulha</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>yeek</t>
+          <t>wisp</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>イーク</t>
+          <t>ウィスプ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>yith</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2830,51 +2830,51 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Yith</t>
+          <t>Galinha</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>yith</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>イス</t>
+          <t>鶏</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>octopus</t>
+          <t>stalker</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EA 23.116</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Polvo</t>
+          <t>Perseguidor</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>octopus</t>
+          <t>stalker</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>タコ</t>
+          <t>ストーカー</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>yeek</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2884,24 +2884,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cavalo</t>
+          <t>Yeek</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>yeek</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>馬</t>
+          <t>イーク</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>quickling</t>
+          <t>yith</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2911,51 +2911,51 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Veloz</t>
+          <t>Yith</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>quickling</t>
+          <t>yith</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>クイックリング</t>
+          <t>イス</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>octopus</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.116</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Polvo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>octopus</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>メタル</t>
+          <t>タコ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2965,24 +2965,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Moto</t>
+          <t>Cavalo</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>バイク</t>
+          <t>馬</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>quickling</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2992,51 +2992,51 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Veloz</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>quickling</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>魚</t>
+          <t>クイックリング</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>animal</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Alpha 20.40</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Porco</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>pig</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>豚</t>
+          <t>メタル</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>catgod</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3046,24 +3046,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Deus Gato</t>
+          <t>Moto</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>catgod</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>猫の神</t>
+          <t>バイク</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>machinegod</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3073,51 +3073,51 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Deus Máquina</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>machinegod</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>機械の神</t>
+          <t>魚</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>undeadgod</t>
+          <t>animal</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.40</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Deus dos Mortos</t>
+          <t>Porco</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>undeadgod</t>
+          <t>pig</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>死霊の神</t>
+          <t>豚</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>catsister</t>
+          <t>catgod</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3127,96 +3127,177 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irmã Gata</t>
+          <t>Deus Gato</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>catsister</t>
+          <t>catgod</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>妹猫</t>
+          <t>猫の神</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>demon</t>
+          <t>machinegod</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EA 23.97</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Demônio</t>
+          <t>Deus Máquina</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>demon</t>
+          <t>machinegod</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>悪魔</t>
+          <t>機械の神</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>servant</t>
+          <t>undeadgod</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alpha 20.64</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Apóstolo</t>
+          <t>Deus dos Mortos</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>apostle</t>
+          <t>undeadgod</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>使徒</t>
+          <t>死霊の神</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>catsister</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Alpha 11.1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Irmã Gata</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>catsister</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>妹猫</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>demon</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EA 23.97</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Demônio</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>demon</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>悪魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>servant</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Alpha 20.64</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Apóstolo</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>apostle</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>使徒</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>god</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Alpha 20.27</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Deus</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>god</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>神</t>
         </is>

--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Race.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Race.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -1293,88 +1293,88 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ratkin</t>
+          <t>goblin</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EA 23.289</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ratoide</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ratkin</t>
+          <t>goblin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ラトキン</t>
+          <t>ゴブリン</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>werewolf</t>
+          <t>kobolt</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EA 23.293</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lobisomem</t>
+          <t>Kobold</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>werewolf</t>
+          <t>kobold</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>人狼</t>
+          <t>コボルト</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>goblin</t>
+          <t>orc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Orc</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>goblin</t>
+          <t>orc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ゴブリン</t>
+          <t>オーク</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kobolt</t>
+          <t>troll</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1384,24 +1384,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kobold</t>
+          <t>Troll</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>kobold</t>
+          <t>troll</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>コボルト</t>
+          <t>トロール</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>lizardman</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1411,24 +1411,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orc</t>
+          <t>Homem-Lagarto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>lizardman</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>オーク</t>
+          <t>リザードマン</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>troll</t>
+          <t>minotaur</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1438,24 +1438,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Troll</t>
+          <t>Minotauro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>troll</t>
+          <t>minotaur</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>トロール</t>
+          <t>ミノタウロス</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lizardman</t>
+          <t>norland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1465,24 +1465,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Homem-Lagarto</t>
+          <t>Norlandês</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>lizardman</t>
+          <t>norland</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>リザードマン</t>
+          <t>ノーランド</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>minotaur</t>
+          <t>asura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1492,51 +1492,66 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minotauro</t>
+          <t>Asura</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>minotaur</t>
+          <t>asura</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ミノタウロス</t>
+          <t>阿修羅</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>norland</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.278</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norlandês</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>norland</t>
+          <t>slime</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ノーランド</t>
+          <t>スライム</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Slimes são seres amorfos e gelatinosos, com corpos que não possuem forma fixa. Podem parecer frágeis e são frequentemente chamados de os monstros mais fracos, mas possuem um potencial misterioso de absorver tudo o que ingerem e transformá-lo em sua própria força. Mesmo que você um dia acordasse como um slime, não haveria motivo para desespero. Aquele corpo humilde é apenas o começo de um caminho sem fim de evolução.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>asura</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1546,66 +1561,51 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Asura</t>
+          <t>Lobo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>asura</t>
+          <t>wolf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>阿修羅</t>
+          <t>狼</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EA 23.278</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>Zumbi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>slime</t>
+          <t>zombie</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>スライム</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Slimes são seres amorfos e gelatinosos, com corpos que não possuem forma fixa. Podem parecer frágeis e são frequentemente chamados de os monstros mais fracos, mas possuem um potencial misterioso de absorver tudo o que ingerem e transformá-lo em sua própria força. Mesmo que você um dia acordasse como um slime, não haveria motivo para desespero. Aquele corpo humilde é apenas o começo de um caminho sem fim de evolução.</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
+          <t>ゾンビ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1615,24 +1615,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lobo</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>wolf</t>
+          <t>rabbit</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>狼</t>
+          <t>ウサギ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1642,24 +1642,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zumbi</t>
+          <t>Ovelha</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>zombie</t>
+          <t>sheep</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ゾンビ</t>
+          <t>羊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>rabbit</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1669,51 +1669,51 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>rabbit</t>
+          <t>frog</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ウサギ</t>
+          <t>蛙</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rabbitkin</t>
+          <t>centipede</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EA 23.289</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>raviano</t>
+          <t>Centopeia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ravian</t>
+          <t>centipede</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ラビアン</t>
+          <t>ムカデ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sheep</t>
+          <t>mandrake</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1723,51 +1723,51 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ovelha</t>
+          <t>Mandrágora</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sheep</t>
+          <t>mandrake</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>羊</t>
+          <t>マンドレイク</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>frog</t>
+          <t>beetle</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.27 fix 2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Besouro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>frog</t>
+          <t>beetle</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>蛙</t>
+          <t>甲虫</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>centipede</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1777,24 +1777,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Centopeia</t>
+          <t>Cogumelo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>centipede</t>
+          <t>mushroom</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ムカデ</t>
+          <t>きのこ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mandrake</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1804,51 +1804,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mandrágora</t>
+          <t>Morcego</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>mandrake</t>
+          <t>bat</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>マンドレイク</t>
+          <t>コウモリ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>beetle</t>
+          <t>ent</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EA 23.27 fix 2</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Besouro</t>
+          <t>Ent</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>beetle</t>
+          <t>ent</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>甲虫</t>
+          <t>エント</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>hound</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1858,24 +1858,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cogumelo</t>
+          <t>Cão de Caça</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>mushroom</t>
+          <t>hound</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>きのこ</t>
+          <t>猟犬</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bat</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1885,24 +1885,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morcego</t>
+          <t>Fantasma</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>bat</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>コウモリ</t>
+          <t>幽霊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ent</t>
+          <t>spirit</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1912,24 +1912,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ent</t>
+          <t>Espírito</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ent</t>
+          <t>spirit</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>エント</t>
+          <t>精霊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hound</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1939,24 +1939,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cão de Caça</t>
+          <t>Olho</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>hound</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>猟犬</t>
+          <t>目</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>wyvern</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fantasma</t>
+          <t>Guiverno</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ghost</t>
+          <t>wyvern</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>幽霊</t>
+          <t>ワイバーン</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>spirit</t>
+          <t>wasp</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Espírito</t>
+          <t>Vespa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>spirit</t>
+          <t>wasp</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>精霊</t>
+          <t>ワスプ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2020,24 +2020,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Olho</t>
+          <t>Gigante</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>giant</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>目</t>
+          <t>巨人</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>wyvern</t>
+          <t>imp</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2047,24 +2047,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Guiverno</t>
+          <t>Diabrete</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>wyvern</t>
+          <t>imp</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ワイバーン</t>
+          <t>インプ</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>wasp</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2074,24 +2074,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vespa</t>
+          <t>Mão</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>wasp</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ワスプ</t>
+          <t>手</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2101,24 +2101,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gigante</t>
+          <t>Cobra</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>giant</t>
+          <t>snake</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>巨人</t>
+          <t>蛇</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>imp</t>
+          <t>drake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2128,24 +2128,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Diabrete</t>
+          <t>Draco</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>imp</t>
+          <t>drake</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>インプ</t>
+          <t>ドレイク</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2155,24 +2155,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mão</t>
+          <t>Urso</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bear</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>手</t>
+          <t>熊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2182,24 +2182,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cobra</t>
+          <t>Armadura</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>snake</t>
+          <t>armor</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>蛇</t>
+          <t>鎧</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>drake</t>
+          <t>medusa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2209,24 +2209,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Draco</t>
+          <t>Medusa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>drake</t>
+          <t>medusa</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ドレイク</t>
+          <t>メデューサ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>cupid</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Urso</t>
+          <t>Cupido</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>bear</t>
+          <t>cupid</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>キューピット</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>phantom</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2263,24 +2263,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Armadura</t>
+          <t>Fantasma Sombrio</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>armor</t>
+          <t>phantom</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>鎧</t>
+          <t>ファントム</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>medusa</t>
+          <t>harpy</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2290,24 +2290,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Medusa</t>
+          <t>Hárpia</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medusa</t>
+          <t>harpy</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>メデューサ</t>
+          <t>ハーピー</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cupid</t>
+          <t>dragon</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2317,24 +2317,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cupido</t>
+          <t>Dragão</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cupid</t>
+          <t>dragon</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>キューピット</t>
+          <t>ドラゴン</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>phantom</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2344,24 +2344,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fantasma Sombrio</t>
+          <t>Dinossauro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>phantom</t>
+          <t>dinosaur</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ファントム</t>
+          <t>恐竜</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>harpy</t>
+          <t>cerberus</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2371,24 +2371,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hárpia</t>
+          <t>Cérbero</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>harpy</t>
+          <t>cerberus</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ハーピー</t>
+          <t>ケルベロス</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>spider</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2398,24 +2398,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dragão</t>
+          <t>Aranha</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dragon</t>
+          <t>spider</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ドラゴン</t>
+          <t>蜘蛛</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dinosaur</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2425,24 +2425,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dinossauro</t>
+          <t>Rocha</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>dinosaur</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>恐竜</t>
+          <t>岩</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cerberus</t>
+          <t>crab</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2452,24 +2452,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cérbero</t>
+          <t>Caranguejo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>cerberus</t>
+          <t>crab</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ケルベロス</t>
+          <t>蟹</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>spider</t>
+          <t>skeleton</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Aranha</t>
+          <t>Esqueleto</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>spider</t>
+          <t>skeleton</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>蜘蛛</t>
+          <t>骸骨</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2506,24 +2506,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rocha</t>
+          <t>Peça</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>rock</t>
+          <t>piece</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>岩</t>
+          <t>駒</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>crab</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2533,24 +2533,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Caranguejo</t>
+          <t>Gato</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>crab</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>蟹</t>
+          <t>猫</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>skeleton</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2560,24 +2560,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Esqueleto</t>
+          <t>Cachorro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>skeleton</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>骸骨</t>
+          <t>犬</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>roran</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2587,51 +2587,51 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Peça</t>
+          <t>Roran</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>piece</t>
+          <t>roran</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>駒</t>
+          <t>ローラン</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>mermaid</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.64</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gato</t>
+          <t>Sereia</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>mermaid</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>猫</t>
+          <t>人魚</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>rat</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2641,24 +2641,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cachorro</t>
+          <t>Rato</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>rat</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>犬</t>
+          <t>ねずみ</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>roran</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2668,51 +2668,51 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Roran</t>
+          <t>Concha</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>roran</t>
+          <t>shell</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ローラン</t>
+          <t>やどかり</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mermaid</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alpha 20.64</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sereia</t>
+          <t>Máquina</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>mermaid</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>人魚</t>
+          <t>機械</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rat</t>
+          <t>wisp</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2722,24 +2722,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rato</t>
+          <t>Fagulha</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>rat</t>
+          <t>wisp</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ねずみ</t>
+          <t>ウィスプ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2749,24 +2749,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Concha</t>
+          <t>Galinha</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>shell</t>
+          <t>chicken</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>やどかり</t>
+          <t>鶏</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>stalker</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2776,24 +2776,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Máquina</t>
+          <t>Perseguidor</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>stalker</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>機械</t>
+          <t>ストーカー</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>wisp</t>
+          <t>yeek</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2803,24 +2803,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fagulha</t>
+          <t>Yeek</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>wisp</t>
+          <t>yeek</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ウィスプ</t>
+          <t>イーク</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>yith</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2830,51 +2830,51 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Galinha</t>
+          <t>Yith</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>chicken</t>
+          <t>yith</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>鶏</t>
+          <t>イス</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>stalker</t>
+          <t>octopus</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.116</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Perseguidor</t>
+          <t>Polvo</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>stalker</t>
+          <t>octopus</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ストーカー</t>
+          <t>タコ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>yeek</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2884,24 +2884,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yeek</t>
+          <t>Cavalo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>yeek</t>
+          <t>horse</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>イーク</t>
+          <t>馬</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>yith</t>
+          <t>quickling</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2911,51 +2911,51 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Yith</t>
+          <t>Veloz</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>yith</t>
+          <t>quickling</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>イス</t>
+          <t>クイックリング</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>octopus</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EA 23.116</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Polvo</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>octopus</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>タコ</t>
+          <t>メタル</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2965,24 +2965,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cavalo</t>
+          <t>Moto</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>horse</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>馬</t>
+          <t>バイク</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>quickling</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2992,51 +2992,51 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Veloz</t>
+          <t>Peixe</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>quickling</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>クイックリング</t>
+          <t>魚</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>animal</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.40</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Porco</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>metal</t>
+          <t>pig</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>メタル</t>
+          <t>豚</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>catgod</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3046,24 +3046,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Moto</t>
+          <t>Deus Gato</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>bike</t>
+          <t>catgod</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>バイク</t>
+          <t>猫の神</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>machinegod</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3073,51 +3073,51 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Peixe</t>
+          <t>Deus Máquina</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>machinegod</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>魚</t>
+          <t>機械の神</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>animal</t>
+          <t>undeadgod</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Alpha 20.40</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Porco</t>
+          <t>Deus dos Mortos</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>pig</t>
+          <t>undeadgod</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>豚</t>
+          <t>死霊の神</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>catgod</t>
+          <t>catsister</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3127,177 +3127,96 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Deus Gato</t>
+          <t>Irmã Gata</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>catgod</t>
+          <t>catsister</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>猫の神</t>
+          <t>妹猫</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>machinegod</t>
+          <t>demon</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.97</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Deus Máquina</t>
+          <t>Demônio</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>machinegod</t>
+          <t>demon</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>機械の神</t>
+          <t>悪魔</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>undeadgod</t>
+          <t>servant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.64</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Deus dos Mortos</t>
+          <t>Apóstolo</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>undeadgod</t>
+          <t>apostle</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>死霊の神</t>
+          <t>使徒</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>catsister</t>
+          <t>god</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.27</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irmã Gata</t>
+          <t>Deus</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>catsister</t>
+          <t>god</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
-        <is>
-          <t>妹猫</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>demon</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>EA 23.97</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Demônio</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>demon</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>悪魔</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>servant</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Alpha 20.64</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Apóstolo</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>apostle</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>使徒</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>god</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Alpha 20.27</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Deus</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>god</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
         <is>
           <t>神</t>
         </is>
